--- a/Data/Bronze/MCIC.INVESTIGACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 12. RECURSOS FÍSICOS Y TECNOLÓGICOS/c. Socialización con la comunidad académica de acciones y avances/F12_Estudiantes_activos_por_enfasis_Investigacion.xlsx
+++ b/Data/Bronze/MCIC.INVESTIGACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 12. RECURSOS FÍSICOS Y TECNOLÓGICOS/c. Socialización con la comunidad académica de acciones y avances/F12_Estudiantes_activos_por_enfasis_Investigacion.xlsx
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -586,7 +586,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Soporte de la última diapositiva («Estudiantes impactados») de la presentación de laboratorios. Misma información que la diapositiva, más el detalle de las otras modalidades para contexto.</t>
+          <t>Soporte de la última diapositiva («Estudiantes impactados») de la presentación de laboratorios. Misma información que la diapositiva, más el detalle de la otra modalidad para contexto. Investigación incluye a los estudiantes del plan anterior.</t>
         </is>
       </c>
     </row>
@@ -664,26 +664,18 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Plan anterior sin modalidad en 2022</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
           <t>Énfasis con estudiantes</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="9" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>158</v>
+        <v>209</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>51</v>
-      </c>
-      <c r="G10" s="9" t="n">
         <v>6</v>
       </c>
     </row>
@@ -733,13 +725,13 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>26</v>
@@ -755,7 +747,7 @@
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C16" s="11" t="n">
         <v>1</v>
@@ -777,13 +769,13 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>26</v>
@@ -799,19 +791,19 @@
         </is>
       </c>
       <c r="B18" s="11" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -865,415 +857,241 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
+        <v>209</v>
+      </c>
+      <c r="C21" s="6" t="n">
         <v>158</v>
       </c>
-      <c r="C21" s="6" t="n">
-        <v>135</v>
-      </c>
       <c r="D21" s="6" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>Plan anterior sin modalidad (aparte)</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="n">
-        <v>51</v>
-      </c>
-      <c r="C22" s="11" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Contexto — Profundización</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Énfasis</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Teleinformática</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="C25" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Sistemas de Información</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Geomática</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Ingeniería de Software</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Inteligencia Artificial</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Sin énfasis definido aún</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E22" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Contexto — Profundización</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Énfasis</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Teleinformática</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Sistemas de Información</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C27" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D27" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Geomática</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>Ingeniería de Software</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="n">
-        <v>47</v>
-      </c>
-      <c r="C29" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>38</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Inteligencia Artificial</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>12</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>Sin énfasis definido aún</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B31" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="C32" s="6" t="n">
+      <c r="C31" s="6" t="n">
         <v>89</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D31" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E31" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F31" s="6" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Contexto — Plan anterior (sin modalidad)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>Énfasis</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E35" s="10" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Teleinformática</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="C36" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D36" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>Sistemas de Información</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Geomática</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="C38" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>Ingeniería de Software</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="C39" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="D39" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="C40" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="D40" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" ht="52" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
+    <row r="33" ht="52" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>Estudiantes con matrícula vigente en el año (entre su ingreso y su última matrícula en Cóndor). Fuente: Cóndor y bases de datos MCIC. Un estudiante cuenta una vez por año; el énfasis es el de su plan de ingreso. Es una aproximación: no se conocen los periodos intermedios sin matrícula. «Sin énfasis definido aún»: estudiantes de los proyectos 595/695 que no aparecen con énfasis en las bases MCIC (cohortes recientes).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A6:B6"/>
+  <mergeCells count="18">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="A23:H23"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="C7:H7"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C5:H5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A6:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
